--- a/artfynd/A 22580-2024 artfynd.xlsx
+++ b/artfynd/A 22580-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130184339</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22580-2024 artfynd.xlsx
+++ b/artfynd/A 22580-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130184339</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22580-2024 artfynd.xlsx
+++ b/artfynd/A 22580-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130184339</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22580-2024 artfynd.xlsx
+++ b/artfynd/A 22580-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>130184339</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -814,6 +814,148 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130184586</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hultamossen, Hultamossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>485109</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6556344</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hack i död gran</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
